--- a/Proyecto_integrador/BaseDeDatos_Facturate.xlsx
+++ b/Proyecto_integrador/BaseDeDatos_Facturate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30607"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tecnica CESDE\Semestre 2\Proyecto_integrador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{601DA7EA-E70C-4481-B1CF-67F241EE47D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B1CC664-9C93-4772-B61A-FAD6C86E85A1}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{601DA7EA-E70C-4481-B1CF-67F241EE47D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{880CA77D-DE0C-4DD7-9667-3E6E644AAC8C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="3" xr2:uid="{497C08C4-B0EA-4704-A0CD-30478E7AC752}"/>
   </bookViews>
@@ -18,6 +18,9 @@
     <sheet name="VENTAS" sheetId="3" r:id="rId3"/>
     <sheet name="CATÁLOGO E INVENTARIO" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CATÁLOGO E INVENTARIO'!$B$39:$D$49</definedName>
+  </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -133,7 +136,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="148">
   <si>
     <t>USUARIOS Y NEGOCIO</t>
   </si>
@@ -575,9 +578,6 @@
     <t>Devolucion_ID</t>
   </si>
   <si>
-    <t>TiposMovimiento</t>
-  </si>
-  <si>
     <t>Efecto_Movimiento</t>
   </si>
   <si>
@@ -599,9 +599,6 @@
     <t>Activa</t>
   </si>
   <si>
-    <t>TipoAlerta</t>
-  </si>
-  <si>
     <t>Descripcion_Alerta</t>
   </si>
   <si>
@@ -609,6 +606,18 @@
   </si>
   <si>
     <t>NOT NULL DEFAULT 'MEDIA'</t>
+  </si>
+  <si>
+    <t>TiposMovimientos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>AlertasInventario</t>
+  </si>
+  <si>
+    <t>TiposAlerta</t>
   </si>
 </sst>
 </file>
@@ -711,12 +720,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="10">
@@ -827,31 +842,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -859,17 +859,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -882,6 +873,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -901,22 +895,22 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -928,6 +922,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFCCFF"/>
+      <color rgb="FF9966FF"/>
       <color rgb="FF00D661"/>
     </mruColors>
   </colors>
@@ -1251,425 +1247,435 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="str">
+      <c r="A1" s="18" t="str">
         <f>UPPER("1. Arquitectura general de Facturate")</f>
         <v>1. ARQUITECTURA GENERAL DE FACTURATE</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="D4" s="8" t="s">
+      <c r="B4" s="18"/>
+      <c r="D4" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="18"/>
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="12"/>
+      <c r="B8" s="22"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9">
+      <c r="A9" s="4">
         <v>1</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9">
+      <c r="A10" s="4">
         <v>2</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9">
+      <c r="A11" s="4">
         <v>3</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+      <c r="A12" s="4">
         <v>4</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
+      <c r="A13" s="4">
         <v>5</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9">
+      <c r="A14" s="4">
         <v>6</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
+      <c r="A15" s="5">
         <v>7</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="12"/>
+      <c r="B18" s="22"/>
     </row>
     <row r="19" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
+      <c r="A19" s="4">
         <v>1</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9">
+      <c r="A20" s="4">
         <v>2</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9">
+      <c r="A21" s="4">
         <v>3</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9">
+      <c r="A22" s="4">
         <v>4</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
+      <c r="A23" s="5">
         <v>5</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="7"/>
+      <c r="B26" s="20"/>
     </row>
     <row r="27" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3" t="s">
+      <c r="A27" s="4"/>
+      <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3" t="s">
+      <c r="A28" s="4"/>
+      <c r="B28" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3" t="s">
+      <c r="A29" s="4"/>
+      <c r="B29" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3" t="s">
+      <c r="A30" s="4"/>
+      <c r="B30" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
-      <c r="B31" s="5" t="s">
+      <c r="A31" s="5"/>
+      <c r="B31" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="12"/>
+      <c r="B34" s="22"/>
     </row>
     <row r="35" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="B35" s="3" t="s">
+      <c r="A35" s="4">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3" t="s">
+      <c r="A36" s="4">
+        <v>2</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3" t="s">
+      <c r="A37" s="4">
+        <v>3</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3" t="s">
+      <c r="A38" s="4">
+        <v>4</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3" t="s">
+      <c r="A39" s="4">
+        <v>5</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3" t="s">
+      <c r="A40" s="4">
+        <v>6</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-      <c r="B41" s="5" t="s">
+      <c r="A41" s="5">
+        <v>7</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="44" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="7"/>
+      <c r="B44" s="20"/>
     </row>
     <row r="45" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3" t="s">
+      <c r="A45" s="4"/>
+      <c r="B45" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2"/>
-      <c r="B46" s="3" t="s">
+      <c r="A46" s="4"/>
+      <c r="B46" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5" t="s">
+      <c r="A47" s="5"/>
+      <c r="B47" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="50" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B50" s="7"/>
+      <c r="B50" s="20"/>
     </row>
     <row r="51" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2"/>
-      <c r="B51" s="3" t="s">
+      <c r="A51" s="4"/>
+      <c r="B51" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2"/>
-      <c r="B52" s="3" t="s">
+      <c r="A52" s="4"/>
+      <c r="B52" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
-      <c r="B53" s="3" t="s">
+      <c r="A53" s="4"/>
+      <c r="B53" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2"/>
-      <c r="B54" s="3" t="s">
+      <c r="A54" s="4"/>
+      <c r="B54" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="4"/>
-      <c r="B55" s="5" t="s">
+      <c r="A55" s="5"/>
+      <c r="B55" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="58" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B58" s="7"/>
+      <c r="B58" s="20"/>
     </row>
     <row r="59" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2"/>
-      <c r="B59" s="3" t="s">
+      <c r="A59" s="4"/>
+      <c r="B59" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="3" t="s">
+      <c r="A60" s="4"/>
+      <c r="B60" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
-      <c r="B61" s="3" t="s">
+      <c r="A61" s="4"/>
+      <c r="B61" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
-      <c r="B62" s="3" t="s">
+      <c r="A62" s="4"/>
+      <c r="B62" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5" t="s">
+      <c r="A63" s="5"/>
+      <c r="B63" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="66" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B66" s="7"/>
+      <c r="B66" s="20"/>
     </row>
     <row r="67" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2"/>
-      <c r="B67" s="3" t="s">
+      <c r="A67" s="4"/>
+      <c r="B67" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="4"/>
-      <c r="B68" s="5" t="s">
+      <c r="A68" s="5"/>
+      <c r="B68" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="71" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B71" s="7"/>
+      <c r="B71" s="20"/>
     </row>
     <row r="72" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="4"/>
-      <c r="B72" s="5" t="s">
+      <c r="A72" s="5"/>
+      <c r="B72" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="75" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B75" s="7"/>
+      <c r="B75" s="20"/>
     </row>
     <row r="76" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2"/>
-      <c r="B76" s="3" t="s">
+      <c r="A76" s="4"/>
+      <c r="B76" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2"/>
-      <c r="B77" s="3" t="s">
+      <c r="A77" s="4"/>
+      <c r="B77" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2"/>
-      <c r="B78" s="3" t="s">
+      <c r="A78" s="4"/>
+      <c r="B78" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="4"/>
-      <c r="B79" s="5" t="s">
+      <c r="A79" s="5"/>
+      <c r="B79" s="3" t="s">
         <v>47</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="13">
-    <mergeCell ref="A1:H3"/>
-    <mergeCell ref="A4:B6"/>
-    <mergeCell ref="D4:E6"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A50:B50"/>
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A71:B71"/>
@@ -1678,6 +1684,11 @@
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A1:H3"/>
+    <mergeCell ref="A4:B6"/>
+    <mergeCell ref="D4:E6"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A50:B50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A8:B8" location="'USUARIOS Y NEGOCIO'!F1C1" display="USUARIOS Y NEGOCIO" xr:uid="{473909FA-D6EC-4D95-AE5A-411BEF145850}"/>
@@ -1693,485 +1704,485 @@
   <dimension ref="B1:K53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="13" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="13" customWidth="1"/>
-    <col min="6" max="8" width="17.7109375" style="13" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" style="13" customWidth="1"/>
-    <col min="10" max="12" width="17.7109375" style="13" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" style="13" customWidth="1"/>
-    <col min="14" max="16" width="17.7109375" style="13" customWidth="1"/>
-    <col min="17" max="16384" width="11.42578125" style="13"/>
+    <col min="1" max="1" width="5.7109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" style="6" customWidth="1"/>
+    <col min="6" max="8" width="17.7109375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="5.7109375" style="6" customWidth="1"/>
+    <col min="10" max="12" width="17.7109375" style="6" customWidth="1"/>
+    <col min="13" max="13" width="5.7109375" style="6" customWidth="1"/>
+    <col min="14" max="16" width="17.7109375" style="6" customWidth="1"/>
+    <col min="17" max="16384" width="11.42578125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="27"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" spans="2:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="28"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="30"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
     </row>
     <row r="4" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
     </row>
     <row r="5" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="16" t="s">
+      <c r="C7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="16" t="s">
+      <c r="C8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" s="17"/>
+      <c r="D9" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="9"/>
     </row>
     <row r="10" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
     </row>
     <row r="13" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="18" t="s">
+      <c r="C14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="18" t="s">
+      <c r="C16" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="18" t="s">
+      <c r="C17" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
     </row>
     <row r="20" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="18" t="s">
+      <c r="C21" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="18" t="s">
+      <c r="C22" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C23" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="18" t="s">
+      <c r="C23" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
     </row>
     <row r="26" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C27" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="18" t="s">
+      <c r="C27" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="18" t="s">
+      <c r="C28" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" s="18" t="s">
+      <c r="C29" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C30" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="18" t="s">
+      <c r="C30" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="32" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
     </row>
     <row r="33" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="34" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="35" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="16" t="s">
+      <c r="C35" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="37" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
     </row>
     <row r="38" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="39" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" s="16" t="s">
+      <c r="C39" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="40" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D40" s="16" t="s">
+      <c r="C40" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="41" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" s="16" t="s">
+      <c r="C41" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="42" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C42" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D42" s="16" t="s">
+      <c r="C42" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="43" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="44" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="45" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D45" s="16" t="s">
+      <c r="C45" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="47" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="14" t="s">
+      <c r="B47" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
     </row>
     <row r="48" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="49" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C49" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D49" s="16" t="s">
+      <c r="C49" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="50" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C50" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D50" s="16" t="s">
+      <c r="C50" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="8" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="51" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C51" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51" s="16" t="s">
+      <c r="C51" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D51" s="8" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="16" t="s">
+      <c r="B52" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="53" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="8" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2203,239 +2214,239 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="21"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="22"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
     </row>
     <row r="4" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
     </row>
     <row r="5" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="8" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="16" t="s">
+      <c r="C8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="16" t="s">
+      <c r="C9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="16" t="s">
+      <c r="C10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
     </row>
     <row r="14" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
     </row>
     <row r="15" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="18" t="s">
+      <c r="C16" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="18" t="s">
+      <c r="C17" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="18" t="s">
+      <c r="C18" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="10" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="18" t="s">
+      <c r="C19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
     </row>
     <row r="21" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
     </row>
     <row r="22" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="18" t="s">
+      <c r="C23" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="18" t="s">
+      <c r="C24" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C25" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="18" t="s">
+      <c r="C25" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2451,7 +2462,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADD05439-7A0D-48CB-8899-F6B6F2D3A1AA}">
-  <dimension ref="B1:D72"/>
+  <dimension ref="B1:F72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
@@ -2461,675 +2472,677 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20"/>
-      <c r="D1" s="21"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="22"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
     </row>
     <row r="4" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
     </row>
     <row r="5" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="18" t="s">
+      <c r="C6" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="C7" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="18" t="s">
+      <c r="C8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
     </row>
     <row r="10" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
     </row>
     <row r="11" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="18" t="s">
+      <c r="C12" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="18" t="s">
+      <c r="C14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="18" t="s">
+      <c r="C15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="18" t="s">
+      <c r="C16" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="18" t="s">
+      <c r="C17" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="23" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
     </row>
     <row r="24" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="18" t="s">
+      <c r="C26" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="18" t="s">
+      <c r="C27" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
     </row>
     <row r="31" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="32" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="33" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="18" t="s">
+      <c r="C33" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="34" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="35" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="10" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="36" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="38" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
     </row>
     <row r="39" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="40" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="41" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="42" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="43" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="44" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="45" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D45" s="18" t="s">
+      <c r="C45" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="46" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C46" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D46" s="18" t="s">
+      <c r="C46" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="47" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="10" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="48" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="49" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="18" t="s">
+    <row r="49" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="51" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="14" t="s">
+    <row r="51" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+    </row>
+    <row r="52" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F54" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-    </row>
-    <row r="52" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="15" t="s">
+      <c r="C55" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+    </row>
+    <row r="58" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C58" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D52" s="15" t="s">
+      <c r="D58" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C53" s="16" t="s">
+    <row r="59" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D59" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="16" t="s">
+    <row r="60" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+    </row>
+    <row r="67" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C54" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D54" s="18" t="s">
+      <c r="C69" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D69" s="10" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="D55" s="18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-    </row>
-    <row r="58" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="C62" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D62" s="18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D63" s="18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="18" t="s">
+    <row r="70" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="C70" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="B71" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C72" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D64" s="18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-    </row>
-    <row r="67" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C69" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="C70" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D70" s="18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B71" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="C71" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D72" s="18" t="s">
+      <c r="D72" s="10" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B51:D51"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="B66:D66"/>
     <mergeCell ref="B4:D4"/>
@@ -3138,6 +3151,7 @@
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B51:D51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
